--- a/Dataset/3_label/CLOSING_CLOSING_V4_2.5 divisions_per_second.xlsx
+++ b/Dataset/3_label/CLOSING_CLOSING_V4_2.5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1890,60 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V4_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C82" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V4_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>18200</v>
+      </c>
+      <c r="C83" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CLOSING_CLOSING_V4_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>18400</v>
+      </c>
+      <c r="C84" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
